--- a/backend/data/financials_by_company/1KN.F.xlsx
+++ b/backend/data/financials_by_company/1KN.F.xlsx
@@ -3884,237 +3884,237 @@
       </c>
       <c r="AL1" t="inlineStr">
         <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="AO1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="AP1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="AQ1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="AW1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="AX1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="AY1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
       <c r="AZ1" t="inlineStr">
         <is>
+          <t>sharesOutstanding</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>impliedSharesOutstanding</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>bookValue</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="BF1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="BG1" t="inlineStr">
+        <is>
+          <t>marketCap</t>
+        </is>
+      </c>
+      <c r="BH1" t="inlineStr">
+        <is>
+          <t>priceToBook</t>
+        </is>
+      </c>
+      <c r="BI1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="BJ1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="BK1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="BL1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="BM1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="BN1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="BO1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="BP1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="BQ1" t="inlineStr">
+        <is>
+          <t>financialCurrency</t>
+        </is>
+      </c>
+      <c r="BR1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="BS1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="BT1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="BU1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="BV1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="BW1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="BX1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="BY1" t="inlineStr">
+        <is>
           <t>earningsTimestamp</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>earningsCallTimestampStart</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>earningsCallTimestampEnd</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>epsForward</t>
-        </is>
-      </c>
-      <c r="BH1" t="inlineStr">
-        <is>
-          <t>sharesOutstanding</t>
-        </is>
-      </c>
-      <c r="BI1" t="inlineStr">
-        <is>
-          <t>impliedSharesOutstanding</t>
-        </is>
-      </c>
-      <c r="BJ1" t="inlineStr">
-        <is>
-          <t>bookValue</t>
-        </is>
-      </c>
-      <c r="BK1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="BL1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="BM1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="BN1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="BO1" t="inlineStr">
-        <is>
-          <t>marketCap</t>
-        </is>
-      </c>
-      <c r="BP1" t="inlineStr">
-        <is>
-          <t>priceToBook</t>
-        </is>
-      </c>
-      <c r="BQ1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="BR1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="BS1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="BT1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="BU1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="BV1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="BW1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="BX1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="BY1" t="inlineStr">
-        <is>
-          <t>financialCurrency</t>
-        </is>
-      </c>
-      <c r="BZ1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="CA1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="CB1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="CC1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="CD1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="CE1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="CF1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
       <c r="CG1" t="inlineStr">
@@ -4131,58 +4131,58 @@
         <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>24.15</v>
+        <v>23.7</v>
       </c>
       <c r="D2" t="n">
-        <v>23.6</v>
+        <v>23.25</v>
       </c>
       <c r="E2" t="n">
-        <v>23.6</v>
+        <v>23.25</v>
       </c>
       <c r="F2" t="n">
-        <v>24.05</v>
+        <v>23.25</v>
       </c>
       <c r="G2" t="n">
-        <v>24.15</v>
+        <v>23.7</v>
       </c>
       <c r="H2" t="n">
-        <v>23.6</v>
+        <v>23.25</v>
       </c>
       <c r="I2" t="n">
-        <v>23.6</v>
+        <v>23.25</v>
       </c>
       <c r="J2" t="n">
-        <v>24.05</v>
+        <v>23.25</v>
       </c>
       <c r="K2" t="n">
-        <v>9.581673</v>
+        <v>9.117647</v>
       </c>
       <c r="L2" t="n">
-        <v>11.84729</v>
+        <v>11.453202</v>
       </c>
       <c r="M2" t="n">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="N2" t="n">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="O2" t="n">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="P2" t="n">
-        <v>230</v>
+        <v>164</v>
       </c>
       <c r="Q2" t="n">
-        <v>230</v>
+        <v>164</v>
       </c>
       <c r="R2" t="n">
-        <v>23.55</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>23.8</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>23.02</v>
+        <v>23</v>
       </c>
       <c r="U2" t="n">
         <v>29.21</v>
@@ -4194,16 +4194,16 @@
         <v>9.85</v>
       </c>
       <c r="X2" t="n">
-        <v>24.1736</v>
+        <v>24.218</v>
       </c>
       <c r="Y2" t="n">
-        <v>25.20605</v>
+        <v>24.88035</v>
       </c>
       <c r="Z2" t="n">
         <v>1.783</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.07383023</v>
+        <v>0.075232066</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
@@ -4253,170 +4253,170 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
+          <t>VICI Properties Inc.</t>
+        </is>
+      </c>
+      <c r="AM2" t="n">
+        <v>7200000</v>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>dr_market</t>
+        </is>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>Vici Properties Inc.          R</t>
+        </is>
+      </c>
+      <c r="AR2" t="n">
+        <v>-1.8987373</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AM2" t="n">
-        <v>1780386119</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>-0.41408026</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>24.05</v>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>Vici Properties Inc.          R</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
+      <c r="AU2" t="n">
+        <v>1782109287</v>
+      </c>
+      <c r="AV2" t="inlineStr">
         <is>
           <t>FRA</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>finmb_430871960</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>Europe/Berlin</t>
         </is>
       </c>
-      <c r="AU2" t="inlineStr">
+      <c r="AY2" t="inlineStr">
         <is>
           <t>CEST</t>
         </is>
       </c>
-      <c r="AV2" t="n">
-        <v>7200000</v>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>dr_market</t>
-        </is>
-      </c>
-      <c r="AX2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>VICI Properties Inc.</t>
-        </is>
-      </c>
       <c r="AZ2" t="n">
+        <v>1076780187</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>1076780187</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>22.75151</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>-0.9680004</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>-0.039970286</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>-1.6303501</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>-0.06552761999999999</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>25035139072</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>1.0219102</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>15</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>15</v>
+      </c>
+      <c r="BK2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BL2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>1568700000000</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>-0.45000076</v>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>23.25 - 23.25</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>Frankfurt</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="BR2" t="n">
+        <v>152</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>0.010869565</v>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>23.0 - 29.21</t>
+        </is>
+      </c>
+      <c r="BV2" t="n">
+        <v>-5.959999</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>-0.2040397</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>-14.594597</v>
+      </c>
+      <c r="BY2" t="n">
         <v>1777492800</v>
       </c>
-      <c r="BA2" t="n">
+      <c r="BZ2" t="n">
         <v>1785355200</v>
       </c>
-      <c r="BB2" t="n">
+      <c r="CA2" t="n">
         <v>1785355200</v>
       </c>
-      <c r="BC2" t="n">
+      <c r="CB2" t="n">
         <v>1777557600</v>
       </c>
-      <c r="BD2" t="n">
+      <c r="CC2" t="n">
         <v>1777557600</v>
       </c>
-      <c r="BE2" t="b">
+      <c r="CD2" t="b">
         <v>1</v>
       </c>
-      <c r="BF2" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="BG2" t="n">
+      <c r="CE2" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="CF2" t="n">
         <v>2.03</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>1076780187</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>1076780187</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>22.638222</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>-0.123600006</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>-0.0051130163</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>-1.1560516</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>-0.045864053</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>25896562688</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>1.0623626</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>15</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>15</v>
-      </c>
-      <c r="BS2" t="b">
-        <v>0</v>
-      </c>
-      <c r="BT2" t="b">
-        <v>0</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>1568700000000</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>-0.10000038</v>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>23.6 - 24.05</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>Frankfurt</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="BZ2" t="n">
-        <v>154</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>1.0299988</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>0.044743646</v>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>23.02 - 29.21</t>
-        </is>
-      </c>
-      <c r="CD2" t="n">
-        <v>-5.16</v>
-      </c>
-      <c r="CE2" t="n">
-        <v>-0.17665184</v>
-      </c>
-      <c r="CF2" t="n">
-        <v>-13.066954</v>
       </c>
       <c r="CG2" t="inlineStr"/>
     </row>
